--- a/series_data/the-signal/series_log.xlsx
+++ b/series_data/the-signal/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2227,336 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:21</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7f682389b40de60d75272ed36d8ba146_1782152484.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/42d4e092e25a90bffe53c0828a209bd4_1782152741.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:27</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4f04122b177fc737e9241d962dfec181_1782152846.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:29</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/96848bd711ab0f0049b18f4d8f0cff0f_1782152969.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/420c73f40d62235caf39a8e0b5cee6ae_1782153107.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-22 18:34</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3ded05db93160e1eb5bd9c16544e4db6_1782153279.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep02/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/the-signal/series_log.xlsx
+++ b/series_data/the-signal/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2557,6 +2557,336 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:38</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5a40f23f2cde11c8d638da38cf38fdff_1782236272.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:39</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/56da3ff8cfddb51a7c23cf9a3ff95bf4_1782236381.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:42</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/df698a061cc74337555434cdb970f300_1782236532.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4de9d1e524a0d5893c894a4b2f74dc65_1782236671.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0407d838e7d731a09c03b3add074e225_1782236786.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-23 17:48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f37bc2aee91bc990e63ea0db800245c6_1782236907.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep03/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/the-signal/series_log.xlsx
+++ b/series_data/the-signal/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,336 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:33</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/063ffe8648628873d557b03e530a9c53_1782322378.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:34</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/744a22dae6b7620959813ca6de9422ae_1782322487.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:36</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/df78de734bddec36d15b4aec194d2602_1782322603.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:39</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9d6c58104bef5f74363b0a0c3ae42f30_1782322757.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:41</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8fbdee342c9a3e77a1872a1f0b067bc3_1782322885.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:43</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cfc69f6e38c5c3322b0048767166ac8f_1782323018.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep04/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/the-signal/series_log.xlsx
+++ b/series_data/the-signal/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3217,6 +3217,336 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:41</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/02df06fa6397183c14c61a85c8cfccaa_1782409295.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:44</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9c82ba24349e8777497d3cc745062823_1782409435.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:46</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/43b015b8bc8dcadf55ef9a549fd883b1_1782409573.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:49</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3a5566ec1f8653317cc94ae55820f01d_1782409769.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:52</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bdb5cc29c0df09f8a64d0a54fc842b15_1782409946.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-25 17:55</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0b1f0fae29078263c198b205c0955c27_1782410112.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/the-signal/episodes/ep05/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
